--- a/data/samples/Bradesco-CC-12345.xlsx
+++ b/data/samples/Bradesco-CC-12345.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,12 +448,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PIX RECEBIDO CLIENTE A</t>
+          <t>SALDO INICIAL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>1500</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="3">
@@ -462,12 +462,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PIX ENVIADO FORNECEDOR X</t>
+          <t>PIX RECEBIDO CLIENTE A</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>-800</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="4">
@@ -476,16 +476,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BOLETO PAGAMENTO LUZ</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>BOL-123</t>
-        </is>
-      </c>
+          <t>PIX ENVIADO FORNECEDOR X</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-350</v>
+        <v>-800</v>
       </c>
     </row>
     <row r="5">
@@ -494,16 +490,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TAR LIQ COB</t>
+          <t>BOLETO PAGAMENTO LUZ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>BOL-123</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-3</v>
+        <v>-350</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +513,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -530,44 +526,112 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TED RECEBIDA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>TAR LIQ COB</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="D7" t="n">
-        <v>5000</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DARF FEDERAL</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DARF1</t>
-        </is>
-      </c>
+          <t>TED RECEBIDA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>-1200</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO AUTOMÁTICA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>APL-1</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-3000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
         <v>46147</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>RESGATE FUNDO INVEST</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>RG-1</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DARF FEDERAL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DARF1</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>PIX TAXA EXTRA</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="n">
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="n">
         <v>-45</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SALDO FINAL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>10599</v>
       </c>
     </row>
   </sheetData>
